--- a/output/laminas_provinciales/prov_i_peringrmin_a_2024_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2024_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:19</t>
+    <t xml:space="preserve">2026-09-09 22:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2024_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2024_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:19</t>
+    <t xml:space="preserve">2026-09-17 13:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -955,18 +955,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3.69</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4.12</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="4">
@@ -1015,68 +1015,68 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>4.22</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3.01</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3.69</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4.51</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3.26</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4.12</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="8">

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2024_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2024_los_lagos.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:43</t>
+    <t xml:space="preserve">2026-09-25 21:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -530,7 +530,7 @@
         <v>0.52</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>16.25</v>
+        <v>16.19</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>5</v>
@@ -553,7 +553,7 @@
         <v>0.7</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>35.18</v>
+        <v>35.31</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>5</v>
@@ -576,7 +576,7 @@
         <v>0.63</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>25.2</v>
+        <v>25.33</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>5</v>
@@ -599,7 +599,7 @@
         <v>0.7</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>19.83</v>
+        <v>19.82</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>4</v>
@@ -622,7 +622,7 @@
         <v>0.68</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>26.46</v>
+        <v>26.45</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>4</v>
@@ -642,10 +642,10 @@
         <v>3.01</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.68</v>
+        <v>0.69</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>22.59</v>
+        <v>22.83</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>4</v>
@@ -668,7 +668,7 @@
         <v>0.75</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>20.95</v>
+        <v>20.81</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>3</v>
@@ -688,10 +688,10 @@
         <v>3.01</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>31.56</v>
+        <v>31.8</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>3</v>
@@ -714,7 +714,7 @@
         <v>0.86</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>26.38</v>
+        <v>26.45</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>3</v>
@@ -737,7 +737,7 @@
         <v>0.89</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>21.65</v>
+        <v>21.76</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>2</v>
@@ -760,7 +760,7 @@
         <v>1.04</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>31.14</v>
+        <v>31.2</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>2</v>
@@ -780,10 +780,10 @@
         <v>3.68</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>26.36</v>
+        <v>26.54</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>2</v>
@@ -806,7 +806,7 @@
         <v>1.4</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>24.52</v>
+        <v>24.42</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>1</v>
@@ -829,7 +829,7 @@
         <v>1.51</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>32.61</v>
+        <v>32.64</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1</v>
@@ -852,7 +852,7 @@
         <v>1.46</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>28.68</v>
+        <v>28.7</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>1</v>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2024_los_lagos.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2024_los_lagos.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:42</t>
+    <t xml:space="preserve">2026-10-05 07:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
